--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -76,31 +76,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>APALE</t>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>EVELYN AISHA</t>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
   </si>
   <si>
     <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -618,16 +654,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -641,16 +680,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>61.9</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -664,16 +706,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.08</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -729,16 +774,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>42.42</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -764,7 +809,7 @@
         <v>61.9</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,16 +826,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,16 +877,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920082</v>
+        <v>20330051920093</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -850,53 +895,145 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920358</v>
+        <v>20330051920070</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920069</v>
+        <v>20330051920325</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920081</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920061</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920069</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="G7">
         <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920329</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>MARROQUIN</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -94,15 +91,12 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -115,13 +109,13 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
+    <t>GABRIEL JOSUE</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
@@ -134,6 +128,9 @@
   </si>
   <si>
     <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
   </si>
   <si>
     <t>JUAN GUILLERMO</t>
@@ -877,16 +874,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -895,50 +892,50 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920070</v>
+        <v>20330051920325</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920325</v>
+        <v>20330051920081</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -946,16 +943,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920081</v>
+        <v>20330051920061</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -964,21 +961,21 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920061</v>
+        <v>20330051920069</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -987,21 +984,21 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920069</v>
+        <v>20330051920386</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1010,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1021,10 +1018,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
@@ -915,7 +915,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -961,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1030,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
@@ -984,7 +984,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -76,64 +76,76 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
   </si>
   <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
+    <t>DORA LUZ</t>
   </si>
 </sst>
 </file>
@@ -651,7 +663,7 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>22</v>
@@ -663,7 +675,7 @@
         <v>33.33</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -771,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>63.64</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -797,16 +809,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -823,13 +835,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>81.08</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H4">
         <v>8.1</v>
@@ -842,7 +854,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -874,16 +886,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920087</v>
+        <v>20330051920065</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -892,21 +904,21 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -915,67 +927,67 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920081</v>
+        <v>20330051920328</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920061</v>
+        <v>20330051920330</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920069</v>
+        <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -984,27 +996,27 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920386</v>
+        <v>20330051920317</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1012,16 +1024,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920329</v>
+        <v>20330051920325</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1030,6 +1042,29 @@
         <v>11</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920335</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
